--- a/data/trans_orig/IP16B_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP16B_2023-Habitat-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>110094</t>
+          <t>109553</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>114612</t>
+          <t>114283</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,49 +745,49 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>99,37%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>133176</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>128944</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>134478</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>98,7%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>95,56%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
           <t>99,66%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>133176</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>129435</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>134490</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>98,7%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>95,93%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>99,67%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>353</t>
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>242498</t>
+          <t>242268</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>248385</t>
+          <t>248458</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>720</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>5450</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,47 +858,47 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>4,74%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1754</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>452</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5986</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>4,27%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1754</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>440</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>5495</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1548</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7435</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>184048</t>
+          <t>184209</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>189227</t>
+          <t>188940</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>240289</t>
+          <t>240637</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>248435</t>
+          <t>248538</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>427075</t>
+          <t>427943</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>436521</t>
+          <t>436660</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>762</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5654</t>
+          <t>5493</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11363</t>
+          <t>11015</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4833</t>
+          <t>4694</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14279</t>
+          <t>13411</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>178396</t>
+          <t>179169</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>186344</t>
+          <t>186460</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>174680</t>
+          <t>174800</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>180978</t>
+          <t>180936</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>356300</t>
+          <t>357018</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>365761</t>
+          <t>366144</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>1495</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9559</t>
+          <t>8786</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1786</t>
+          <t>1828</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8084</t>
+          <t>7964</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>4575</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14419</t>
+          <t>13701</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>159851</t>
+          <t>159776</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>164777</t>
+          <t>164783</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>175891</t>
+          <t>175607</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>338405</t>
+          <t>338711</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>345665</t>
+          <t>345668</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>589</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5521</t>
+          <t>5596</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5631</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>942</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8205</t>
+          <t>7899</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>641840</t>
+          <t>641857</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>651686</t>
+          <t>651919</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>730668</t>
+          <t>730188</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>741879</t>
+          <t>741701</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1375720</t>
+          <t>1375972</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1391436</t>
+          <t>1391602</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6346</t>
+          <t>6113</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16192</t>
+          <t>16175</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8705</t>
+          <t>8883</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19916</t>
+          <t>20396</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17180</t>
+          <t>17014</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32896</t>
+          <t>32644</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16B_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP16B_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>120165</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>117251</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>121238</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>98,8%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>96,41%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>99,68%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>113099</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>109553</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>114283</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>98,34%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>95,26%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>99,37%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>133176</t>
+          <t>117541</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>128944</t>
+          <t>114583</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>134478</t>
+          <t>118652</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>246276</t>
+          <t>237705</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>242268</t>
+          <t>234441</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>248458</t>
+          <t>239514</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1456</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>383</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4370</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>3,59%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1904</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5450</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>4,74%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1754</t>
+          <t>1641</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>530</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5986</t>
+          <t>4599</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>3657</t>
+          <t>3097</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1475</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>6361</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121621</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121621</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121621</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>115003</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>115003</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>115003</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>134930</t>
+          <t>119182</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>134930</t>
+          <t>119182</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>134930</t>
+          <t>119182</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>249933</t>
+          <t>240802</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>249933</t>
+          <t>240802</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>249933</t>
+          <t>240802</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>228278</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>223264</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>230853</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>97,7%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>95,55%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>98,8%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>187579</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>184209</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>188940</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>98,88%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>97,1%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>99,6%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>327</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>245498</t>
+          <t>182023</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>240637</t>
+          <t>179741</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>248538</t>
+          <t>183163</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>433077</t>
+          <t>410301</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>427943</t>
+          <t>405866</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>436660</t>
+          <t>413273</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5378</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2803</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>10392</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>4,45%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2123</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>762</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5493</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6154</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3114</t>
+          <t>386</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11015</t>
+          <t>3808</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>8277</t>
+          <t>6904</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4694</t>
+          <t>3932</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13411</t>
+          <t>11339</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>233656</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>233656</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>233656</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>279</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>189702</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>189702</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>189702</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>339</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>251652</t>
+          <t>183549</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>251652</t>
+          <t>183549</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>251652</t>
+          <t>183549</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>441354</t>
+          <t>417205</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>441354</t>
+          <t>417205</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>441354</t>
+          <t>417205</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>162573</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>159168</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>164477</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>97,98%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>95,93%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>99,13%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>217</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>183641</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>179169</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>186460</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>97,7%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>95,33%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>99,2%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>178782</t>
+          <t>150273</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>174800</t>
+          <t>145716</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>180936</t>
+          <t>152775</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>362423</t>
+          <t>312846</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>357018</t>
+          <t>307004</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>366144</t>
+          <t>316203</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3354</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1450</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>6759</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4,07%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>4314</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1495</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>8786</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3982</t>
+          <t>4288</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>1786</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7964</t>
+          <t>8845</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>8296</t>
+          <t>7642</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4575</t>
+          <t>4285</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13701</t>
+          <t>13484</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165927</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165927</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165927</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>224</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>187955</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>187955</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>187955</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>182764</t>
+          <t>154561</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>182764</t>
+          <t>154561</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>182764</t>
+          <t>154561</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>370719</t>
+          <t>320488</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>370719</t>
+          <t>320488</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>370719</t>
+          <t>320488</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,62 +1749,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>167951</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>163699</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>99,16%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>96,65%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>163334</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>159776</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>164783</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>98,77%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>96,62%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>99,64%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>179725</t>
+          <t>162583</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>175607</t>
+          <t>159373</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>163983</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>343059</t>
+          <t>330535</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>338711</t>
+          <t>326589</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>345668</t>
+          <t>332820</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,69%</t>
         </is>
       </c>
     </row>
@@ -1862,67 +1862,67 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1425</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5677</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3,35%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2038</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>589</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5596</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3,38%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>1912</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>512</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5631</t>
+          <t>5122</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3551</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7899</t>
+          <t>7282</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>165372</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>165372</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>165372</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>164495</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>164495</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>164495</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>346610</t>
+          <t>333871</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>346610</t>
+          <t>333871</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>346610</t>
+          <t>333871</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>941</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>678968</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>672766</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>683176</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>98,32%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>97,42%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>98,93%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>914</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>647654</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>641857</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>651919</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>98,42%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>612419</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>606483</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>616045</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>98,49%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>97,54%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>99,07%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>941</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>737181</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>730188</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>741701</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>98,21%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>97,28%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1384834</t>
+          <t>1291387</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1375972</t>
+          <t>1284136</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1391602</t>
+          <t>1297813</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,89%</t>
         </is>
       </c>
     </row>
@@ -2205,74 +2205,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>11612</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>7404</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>17814</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>10378</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>6113</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>16175</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>9367</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>5741</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>15303</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>2,46%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>13403</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>8883</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>20396</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>2,72%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>43</t>
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>23782</t>
+          <t>20979</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17014</t>
+          <t>14553</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32644</t>
+          <t>28230</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>966</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>690580</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>690580</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>690580</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>932</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>658032</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>658032</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>658032</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>966</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>750584</t>
+          <t>621786</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>750584</t>
+          <t>621786</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>750584</t>
+          <t>621786</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1408616</t>
+          <t>1312366</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1408616</t>
+          <t>1312366</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1408616</t>
+          <t>1312366</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
